--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -85,13 +85,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
   </si>
 </sst>
 </file>
@@ -492,19 +501,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -638,7 +647,7 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -766,19 +775,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -866,7 +875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -898,25 +907,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920141</v>
+        <v>19330051920352</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920334</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,24 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
   </si>
 </sst>
 </file>
@@ -579,19 +561,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +698,7 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -853,19 +835,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -905,52 +887,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920352</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920334</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
@@ -509,19 +509,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -535,19 +535,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -561,19 +561,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>90.63</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -626,16 +626,19 @@
         <v>19</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>19</v>
       </c>
-      <c r="E2">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -649,16 +652,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -672,16 +678,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H4">
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -695,16 +704,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90.63</v>
+      </c>
+      <c r="H5">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -769,7 +781,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -783,19 +795,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -809,19 +821,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -835,19 +847,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>90.63</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -869,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -899,6 +908,29 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920267</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -878,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -908,29 +899,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920267</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
+++ b/docentes/Acevedo Rendón Ismael Arturo - Estadisticos 20212.xlsx
@@ -509,10 +509,10 @@
         <v>20</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>2</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>18</v>
@@ -521,7 +521,7 @@
         <v>90</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -535,10 +535,10 @@
         <v>19</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>18</v>
@@ -547,7 +547,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -561,19 +561,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -652,10 +652,10 @@
         <v>20</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>2</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>18</v>
@@ -664,7 +664,7 @@
         <v>90</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -678,10 +678,10 @@
         <v>19</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>18</v>
@@ -690,7 +690,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -704,19 +704,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -781,7 +781,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -795,19 +795,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,10 +821,10 @@
         <v>19</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>18</v>
@@ -833,7 +833,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -847,19 +847,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
